--- a/artfynd/A 16924-2026 artfynd.xlsx
+++ b/artfynd/A 16924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87060551</v>
+        <v>89807103</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nordost Norrberg, Norrberg, Hls</t>
+          <t>Norrberg, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534663.1729343779</v>
+        <v>534697</v>
       </c>
       <c r="R2" t="n">
-        <v>6904621.786871791</v>
+        <v>6904532</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,30 +769,35 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mats Westberg</t>
+          <t>Helena Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Westberg, Helena Persson</t>
+          <t>Helena Persson, Mats Westberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89807070</v>
+        <v>89807042</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534666.0905281467</v>
+        <v>534715</v>
       </c>
       <c r="R3" t="n">
-        <v>6904565.004658912</v>
+        <v>6904604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,19 +865,9 @@
           <t>2017-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89807042</v>
+        <v>89807070</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534715.1199170145</v>
+        <v>534666</v>
       </c>
       <c r="R4" t="n">
-        <v>6904604.161981691</v>
+        <v>6904565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,19 +976,9 @@
           <t>2017-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-09-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,12 +1019,7 @@
         <v>119802841</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1177,51 +1132,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124349802</v>
+        <v>124349776</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>534634</v>
+        <v>534663</v>
       </c>
       <c r="R6" t="n">
-        <v>6904557</v>
+        <v>6904569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,11 +1208,6 @@
           <t>2025-04-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>1 överblommad blomstängel, 6 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1281,6 +1217,16 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # På sälg</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1300,12 +1246,7 @@
         <v>124349782</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,15 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124349812</v>
+        <v>97567667</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,49 +1365,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>101248</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norrberg, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>534626</v>
+        <v>534771</v>
       </c>
       <c r="R8" t="n">
-        <v>6904546</v>
+        <v>6904513</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1495,17 +1424,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 överblommade blomstänglar, 157 bladrosetter</t>
+          <t>Inventering för länsstyrelsen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,75 +1443,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helena Persson</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Persson, Mats Westberg</t>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124349776</v>
+        <v>97567669</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>101248</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norrberg, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>534663</v>
+        <v>534777</v>
       </c>
       <c r="R9" t="n">
-        <v>6904569</v>
+        <v>6904499</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1606,12 +1531,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Inventering för länsstyrelsen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,39 +1550,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # På sälg</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Persson</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Persson, Mats Westberg</t>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124349790</v>
+        <v>110225690</v>
       </c>
       <c r="B10" t="n">
-        <v>99168</v>
+        <v>43249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,49 +1579,58 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>101248</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrberg, Hls</t>
+          <t>Ångevägen, Norrberg, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>534698</v>
+        <v>534600</v>
       </c>
       <c r="R10" t="n">
-        <v>6904588</v>
+        <v>6904490</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1726,17 +1654,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>6 överblommade blomstänglar, 26 bladrosetter. Samma plats besöktes även 2026-05-02 och har rapporterats som ett separat fynd men positionen ligger inte på exakt samma punkt i kartan. Positionen för fyndet 2026-05-02 bedöms vara noggrannare.</t>
+          <t>Ny lokal. Måttligt till rikligt med ormrot.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,30 +1687,34 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helena Persson</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Persson, Mats Westberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Gustav Wikström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Violett guldvinge X-län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124349824</v>
+        <v>121706649</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,35 +1722,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>101248</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1816,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>534624</v>
+        <v>534749</v>
       </c>
       <c r="R11" t="n">
-        <v>6904547</v>
+        <v>6904578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,17 +1797,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 överblommad blomstängel, 29 bladrosetter</t>
+          <t>2 honor och 1 hane</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,17 +1828,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helena Persson, Mats Westberg</t>
+          <t>Helena Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133149923</v>
+        <v>126411430</v>
       </c>
       <c r="B12" t="n">
-        <v>99168</v>
+        <v>43249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,46 +1846,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>101248</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norrberg, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>534701</v>
+        <v>534739</v>
       </c>
       <c r="R12" t="n">
-        <v>6904577</v>
+        <v>6904503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1961,17 +1904,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>8 överblommade blomställningar, 36 bladrosetter. Samma plats besöktes även 2025-04-21 och har rapporterats som ett separat fynd men positionen ligger inte på exakt samma punkt i kartan. Positionen för fyndet 2026-05-02 bedöms vara noggrannare.</t>
+          <t>17 grader varm, klart väder, 5 m/s, nordöstlig vind, 100% sol. Lokalen som är en sommarstugetomt sköts till stor del med lie-slåtter. Alla violett guldvingar flög inom samma avsnitt på lokalen, därför får dessa samma koordinat.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,22 +1933,1028 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>97567827</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43464</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>201116</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Berggräsfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lasiommata petropolitana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>534764</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6904488</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Inventering för länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>97567665</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ramsjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>534774</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6904489</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-07-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Inventering för länsstyrelsen</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind, Tor Hansson Frank, Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121706546</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norrberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>534715</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6904527</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Helena Persson</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124349790</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norrberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>534698</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6904588</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>6 överblommade blomstänglar, 26 bladrosetter. Samma plats besöktes även 2026-05-02 och har rapporterats som ett separat fynd men positionen ligger inte på exakt samma punkt i kartan. Positionen för fyndet 2026-05-02 bedöms vara noggrannare.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Helena Persson, Mats Westberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124349802</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norrberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>534634</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6904557</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 överblommad blomstängel, 6 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Helena Persson, Mats Westberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124349812</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>534626</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6904546</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5 överblommade blomstänglar, 157 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Helena Persson, Mats Westberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124349824</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>534624</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6904547</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 överblommad blomstängel, 29 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Helena Persson, Mats Westberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133149923</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norrberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>534701</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6904577</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>8 överblommade blomställningar, 36 bladrosetter. Samma plats besöktes även 2025-04-21 och har rapporterats som ett separat fynd men positionen ligger inte på exakt samma punkt i kartan. Positionen för fyndet 2026-05-02 bedöms vara noggrannare.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Helena Persson, Mats Westberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>87060551</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nordost Norrberg, Norrberg, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>534663</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6904622</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mats Westberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mats Westberg, Helena Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16924-2026 artfynd.xlsx
+++ b/artfynd/A 16924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567665</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89807103</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89807042</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89807070</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119802841</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124349776</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124349782</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567667</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1769,6 +1819,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567669</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
           <t>Violett guldvinge X-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110225690</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2036,6 +2096,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121706649</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2156,6 +2221,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126411430</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2266,6 +2336,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121706546</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2381,6 +2456,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124349790</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2496,6 +2576,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124349802</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2611,6 +2696,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124349812</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2726,6 +2816,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124349824</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2841,6 +2936,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133149923</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2955,8 +3055,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87060551</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>